--- a/Result/profitability/5903.xlsx
+++ b/Result/profitability/5903.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>0.19</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8625</v>
+        <v>1.68625</v>
       </c>
       <c r="N2" t="n">
-        <v>35.74875</v>
+        <v>35.645</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.51</v>
+        <v>1.565</v>
       </c>
       <c r="N3" t="n">
-        <v>35.2425</v>
+        <v>35.1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.24</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4125</v>
+        <v>1.48625</v>
       </c>
       <c r="N4" t="n">
-        <v>34.855</v>
+        <v>34.82</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.68</v>
       </c>
       <c r="M5" t="n">
-        <v>1.26375</v>
+        <v>1.375</v>
       </c>
       <c r="N5" t="n">
-        <v>34.51000000000001</v>
+        <v>34.38125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.32</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1075</v>
+        <v>1.15625</v>
       </c>
       <c r="N6" t="n">
-        <v>33.88875</v>
+        <v>33.7675</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.95</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9675</v>
+        <v>1.015</v>
       </c>
       <c r="N7" t="n">
-        <v>33.59375</v>
+        <v>33.59</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>0.87625</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>33.37375</v>
+        <v>33.51375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.65</v>
       </c>
       <c r="M9" t="n">
-        <v>0.80375</v>
+        <v>0.8037500000000001</v>
       </c>
       <c r="N9" t="n">
         <v>33.2075</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5903</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>29228</v>
+      </c>
+      <c r="D75" t="n">
+        <v>18762</v>
+      </c>
+      <c r="E75" t="n">
+        <v>10467</v>
+      </c>
+      <c r="F75" t="n">
+        <v>35.81</v>
+      </c>
+      <c r="G75" t="n">
+        <v>567</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.94%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>93</v>
+      </c>
+      <c r="J75" t="n">
+        <v>660</v>
+      </c>
+      <c r="K75" t="n">
+        <v>550</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.14625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>36.20500000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.120000000000005</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.03228596137215356</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8899999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.5668789808917196</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.030000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.02795874049945712</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
